--- a/data/annonces_contactees.xlsx
+++ b/data/annonces_contactees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1656,9 +1656,6 @@
           <t>SeLoger</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Marseille</t>
@@ -1669,8 +1666,6 @@
           <t>https://www.seloger.com/annonces/locations/appartement/marseille-13/262971937.htm?serp_view=list&amp;search=distributionTypes%3DRent%26estateTypes%3DApartment%26locations%3DAD08FR4491%26numberOfBedroomsMin%3D2%26numberOfRoomsMin%3D4%26priceMax%3D1600%26spaceMin%3D80#ln=classified_search_results&amp;m=classified_search_results_classified_classified_detail_L</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Simule</t>
@@ -1679,6 +1674,115 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>2026-06-03 18:21:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SeLoger</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.seloger.com/annonces/locations/appartement/marseille-4eme-13/les-chartreux/260298553.htm?serp_view=list&amp;search=distributionTypes%3DRent%26estateTypes%3DApartment%26locations%3DAD08FR4491%26numberOfBedroomsMin%3D2%26numberOfRoomsMin%3D4%26priceMax%3D1600%26spaceMin%3D80#ln=classified_search_results&amp;m=classified_search_results_classified_classified_detail_M</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Simule</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:06:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SeLoger</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.seloger.com/annonces/locations/appartement/marseille-12eme-13/les-caillols/270796453.htm?serp_view=list&amp;search=distributionTypes%3DRent%26estateTypes%3DApartment%26locations%3DAD08FR4491%26numberOfBedroomsMin%3D2%26numberOfRoomsMin%3D4%26priceMax%3D1600%26spaceMin%3D80#ln=classified_search_results&amp;m=classified_search_results_classified_classified_detail_L</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Pas de formulaire</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:07:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SeLoger</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.seloger.com/annonces/achat/appartement/saint-denis-93/262871525.htm?serp_view=list&amp;search=distributionTypes%3DBuy%26estateTypes%3DApartment%26locations%3DAD08FR31096%26numberOfBedroomsMin%3D2%26numberOfRoomsMin%3D4%26priceMax%3D70000%26spaceMin%3D80#ln=classified_search_results&amp;m=classified_search_results_classified_classified_detail_M</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Votre bien a retenu toute mon attention.
+Je souhaiterais savoir s'il est toujours disponible et s'il serait possible d'organiser une visite.
+Je reste à votre disposition pour échanger.
+Cordialement</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Contacte</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:24:53</t>
         </is>
       </c>
     </row>

--- a/data/annonces_contactees.xlsx
+++ b/data/annonces_contactees.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -783,6 +783,117 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.seloger.com/annonces/achat/appartement/bordeaux-33/grand-parc-chartrons-paul-doumer/263963347.htm?serp_view=list&amp;search=distributionTypes%3DBuy%26estateTypes%3DApartment%26locations%3DAD08FR13100%26numberOfBedroomsMin%3D1%26numberOfRoomsMin%3D2%26priceMax%3D70000%26spaceMin%3D30#ln=classified_search_results&amp;m=classified_search_results_classified_classified_detail_L</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Appartement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Achat</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>37224</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>24 195</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>775.50</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5908</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3ème étage</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>33000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Votre bien a retenu toute mon attention.
+Je me permets de vous soumettre une offre d'achat a 24 195 €.
+Je reste a votre disposition pour en discuter et organiser une visite.
+Cordialement</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-06-12 18:32:01</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Contacte</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/annonces_contactees.xlsx
+++ b/data/annonces_contactees.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -894,6 +894,228 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.seloger.com/annonces/achat/appartement/bordeaux-33/saint-bruno-saint-augustin/262972505.htm?serp_view=list&amp;search=distributionTypes%3DBuy%26estateTypes%3DApartment%26locations%3DAD08FR13100%26numberOfBedroomsMin%3D1%26numberOfRoomsMin%3D2%26priceMax%3D70000%26spaceMin%3D30#ln=classified_search_results&amp;m=classified_search_results_classified_classified_detail_L</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Appartement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Achat</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18 200</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>425.08</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5908</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>33000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Votre bien a retenu toute mon attention.
+Je me permets de vous soumettre une offre d'achat a 18 200 €.
+Je reste a votre disposition pour en discuter et organiser une visite.
+Cordialement</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-06-12 19:00:58</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Contacte</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.seloger.com/annonces/achat/appartement/le-bouscat-33/cheneraie-lavigne/267977777.htm?serp_view=list&amp;search=distributionTypes%3DBuy%26estateTypes%3DApartment%26locations%3DAD08FR13100%26numberOfBedroomsMin%3D1%26numberOfRoomsMin%3D2%26priceMax%3D70000%26spaceMin%3D30#ln=classified_search_results&amp;m=classified_search_results_classified_classified_detail_L</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Appartement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Achat</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>64131</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>41 685</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>763.46</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6093</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2ème étage</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>33110</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Votre bien a retenu toute mon attention.
+Je me permets de vous soumettre une offre d'achat a 41 685 €.
+Je reste a votre disposition pour en discuter et organiser une visite.
+Cordialement</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-06-12 19:15:08</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Contacte</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
